--- a/sample_data/OrgSight_Sample_OrgChart_28rows.xlsx
+++ b/sample_data/OrgSight_Sample_OrgChart_28rows.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itinfoalvarezandmarsalind-my.sharepoint.com/personal/jagritjain_alvarezandmarsal_com/Documents/Documents/APPS/ORG_ANALYSIS/sample_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F9A1AFDACB6FCA12B72D4C3E9D07A8864FA89CDA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D07FE555-AE11-40DA-967E-64B366011B7A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Census" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -445,8 +451,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,13 +515,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -553,7 +567,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -587,6 +601,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -621,9 +636,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -796,11 +812,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" customWidth="1"/>
+    <col min="11" max="11" width="25.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -909,7 +930,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -965,7 +986,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1021,7 +1042,7 @@
         <v>59000</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1077,7 +1098,7 @@
         <v>53000</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1133,7 +1154,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1189,7 +1210,7 @@
         <v>27600</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1245,7 +1266,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1301,7 +1322,7 @@
         <v>34400</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1357,7 +1378,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1413,7 +1434,7 @@
         <v>17600</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1469,7 +1490,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1525,7 +1546,7 @@
         <v>840000</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1581,7 +1602,7 @@
         <v>19600</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1637,7 +1658,7 @@
         <v>18400</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1693,7 +1714,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1749,7 +1770,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1805,7 +1826,7 @@
         <v>10400</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1861,7 +1882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1917,7 +1938,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -1973,7 +1994,7 @@
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2029,7 +2050,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2085,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2141,7 +2162,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2197,7 +2218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2253,7 +2274,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -2309,7 +2330,7 @@
         <v>8400</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -2365,7 +2386,7 @@
         <v>11600</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>45</v>
       </c>

--- a/sample_data/OrgSight_Sample_OrgChart_28rows.xlsx
+++ b/sample_data/OrgSight_Sample_OrgChart_28rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itinfoalvarezandmarsalind-my.sharepoint.com/personal/jagritjain_alvarezandmarsal_com/Documents/Documents/APPS/ORG_ANALYSIS/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F9A1AFDACB6FCA12B72D4C3E9D07A8864FA89CDA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D07FE555-AE11-40DA-967E-64B366011B7A}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_F9A1AFDACB6FCA12B72D4C3E9D07A8864FA89CDA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8537177-0E0D-455E-8959-AA01F075F80B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="3290" windowWidth="14400" windowHeight="8710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Census" sheetId="1" r:id="rId1"/>
@@ -817,6 +817,11 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="5" max="5" width="34.90625" customWidth="1"/>
+    <col min="6" max="6" width="30.7265625" customWidth="1"/>
+    <col min="7" max="7" width="37.36328125" customWidth="1"/>
+    <col min="8" max="8" width="31.6328125" customWidth="1"/>
     <col min="10" max="10" width="19.453125" customWidth="1"/>
     <col min="11" max="11" width="25.81640625" customWidth="1"/>
   </cols>
